--- a/clang/learn.xlsx
+++ b/clang/learn.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\python\qqstudy\clang\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{375F440F-62DD-47EE-8773-A921F9C71FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{327579EC-E0C5-401E-A02B-6D7B782A16AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15975" xr2:uid="{2ACC17CD-8CFB-485E-B840-8B3BE1E1CA8B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15975" activeTab="1" xr2:uid="{2ACC17CD-8CFB-485E-B840-8B3BE1E1CA8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="39">
   <si>
     <t>列1</t>
   </si>
@@ -125,6 +125,53 @@
   </si>
   <si>
     <t xml:space="preserve">  mov     DWORD PTR [11111111], eax    ; ④ 把 eax 的值（m+n 的结果）写入 x</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>byte 字节</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>丳</t>
+  </si>
+  <si>
+    <t>GB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000MB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000KB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000B</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -132,7 +179,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -154,21 +201,125 @@
       <name val="Wingdings"/>
       <charset val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF34495E"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -177,11 +328,50 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1175,43 +1365,597 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC55DEF7-F911-4BBF-864B-0FC2EE68EC6C}">
-  <dimension ref="L7:N9"/>
+  <dimension ref="L6:AQ35"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="7" spans="12:14" x14ac:dyDescent="0.2">
-      <c r="L7" t="s">
-        <v>15</v>
-      </c>
-      <c r="M7" t="s">
-        <v>15</v>
-      </c>
-      <c r="N7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="12:14" x14ac:dyDescent="0.2">
-      <c r="L8" t="s">
+    <row r="6" spans="12:43" x14ac:dyDescent="0.2">
+      <c r="L6" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="8"/>
+      <c r="T6" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="U6" s="7"/>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7"/>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7"/>
+      <c r="Z6" s="7"/>
+      <c r="AA6" s="8"/>
+      <c r="AB6" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC6" s="7"/>
+      <c r="AD6" s="7"/>
+      <c r="AE6" s="7"/>
+      <c r="AF6" s="7"/>
+      <c r="AG6" s="7"/>
+      <c r="AH6" s="7"/>
+      <c r="AI6" s="8"/>
+      <c r="AJ6" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK6" s="7"/>
+      <c r="AL6" s="7"/>
+      <c r="AM6" s="7"/>
+      <c r="AN6" s="7"/>
+      <c r="AO6" s="7"/>
+      <c r="AP6" s="7"/>
+      <c r="AQ6" s="8"/>
+    </row>
+    <row r="7" spans="12:43" x14ac:dyDescent="0.2">
+      <c r="L7" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="N7" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="O7" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="P7" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q7" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="R7" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="S7" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="T7" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="U7" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="V7" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="W7" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="X7" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y7" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z7" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA7" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB7" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC7" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD7" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE7" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="AF7" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG7" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH7" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI7" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ7" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK7" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL7" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM7" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN7" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO7" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP7" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ7" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="12:43" x14ac:dyDescent="0.2">
+      <c r="L8" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="M8" t="s">
+      <c r="M8" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="N8" t="s">
+      <c r="N8" s="10" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="9" spans="12:14" x14ac:dyDescent="0.2">
-      <c r="L9" t="s">
+      <c r="O8" s="10"/>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="10"/>
+      <c r="S8" s="11"/>
+      <c r="T8" s="9"/>
+      <c r="U8" s="10"/>
+      <c r="V8" s="10"/>
+      <c r="W8" s="10"/>
+      <c r="X8" s="10"/>
+      <c r="Y8" s="10"/>
+      <c r="Z8" s="10"/>
+      <c r="AA8" s="11"/>
+      <c r="AB8" s="9"/>
+      <c r="AC8" s="10"/>
+      <c r="AD8" s="10"/>
+      <c r="AE8" s="10"/>
+      <c r="AF8" s="10"/>
+      <c r="AG8" s="10"/>
+      <c r="AH8" s="10"/>
+      <c r="AI8" s="11"/>
+      <c r="AJ8" s="9"/>
+      <c r="AK8" s="10"/>
+      <c r="AL8" s="10"/>
+      <c r="AM8" s="10"/>
+      <c r="AN8" s="10"/>
+      <c r="AO8" s="10"/>
+      <c r="AP8" s="10"/>
+      <c r="AQ8" s="11"/>
+    </row>
+    <row r="9" spans="12:43" x14ac:dyDescent="0.2">
+      <c r="L9" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="M9" t="s">
+      <c r="M9" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="N9" t="s">
+      <c r="N9" s="13" t="s">
         <v>17</v>
       </c>
+      <c r="O9" s="13"/>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="13"/>
+      <c r="S9" s="14"/>
+      <c r="T9" s="12"/>
+      <c r="U9" s="13"/>
+      <c r="V9" s="13"/>
+      <c r="W9" s="13"/>
+      <c r="X9" s="13"/>
+      <c r="Y9" s="13"/>
+      <c r="Z9" s="13"/>
+      <c r="AA9" s="14"/>
+      <c r="AB9" s="12"/>
+      <c r="AC9" s="13"/>
+      <c r="AD9" s="13"/>
+      <c r="AE9" s="13"/>
+      <c r="AF9" s="13"/>
+      <c r="AG9" s="13"/>
+      <c r="AH9" s="13"/>
+      <c r="AI9" s="14"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="13"/>
+      <c r="AL9" s="13"/>
+      <c r="AM9" s="13"/>
+      <c r="AN9" s="13"/>
+      <c r="AO9" s="13"/>
+      <c r="AP9" s="13"/>
+      <c r="AQ9" s="14"/>
+    </row>
+    <row r="10" spans="12:43" x14ac:dyDescent="0.2">
+      <c r="L10" s="10">
+        <v>0</v>
+      </c>
+      <c r="M10" s="10">
+        <v>0</v>
+      </c>
+      <c r="N10" s="10">
+        <v>0</v>
+      </c>
+      <c r="O10" s="10">
+        <v>0</v>
+      </c>
+      <c r="P10" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="10">
+        <v>0</v>
+      </c>
+      <c r="R10" s="10">
+        <v>0</v>
+      </c>
+      <c r="S10" s="10">
+        <v>0</v>
+      </c>
+      <c r="T10" s="10">
+        <v>0</v>
+      </c>
+      <c r="U10" s="10">
+        <v>0</v>
+      </c>
+      <c r="V10" s="10">
+        <v>0</v>
+      </c>
+      <c r="W10" s="10">
+        <v>0</v>
+      </c>
+      <c r="X10" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AQ10" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="12:43" x14ac:dyDescent="0.2">
+      <c r="L11" s="10">
+        <v>1</v>
+      </c>
+      <c r="M11" s="10">
+        <v>0</v>
+      </c>
+      <c r="N11" s="10">
+        <v>0</v>
+      </c>
+      <c r="O11" s="10">
+        <v>0</v>
+      </c>
+      <c r="P11" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="10">
+        <v>0</v>
+      </c>
+      <c r="R11" s="10">
+        <v>0</v>
+      </c>
+      <c r="S11" s="10">
+        <v>0</v>
+      </c>
+      <c r="T11" s="10">
+        <v>0</v>
+      </c>
+      <c r="U11" s="10">
+        <v>0</v>
+      </c>
+      <c r="V11" s="10">
+        <v>0</v>
+      </c>
+      <c r="W11" s="10">
+        <v>0</v>
+      </c>
+      <c r="X11" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="12:43" x14ac:dyDescent="0.2">
+      <c r="L13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="12:19" x14ac:dyDescent="0.2">
+      <c r="S18" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="12:19" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3">
+        <v>8</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>1</v>
+      </c>
+      <c r="R19" s="3">
+        <v>5</v>
+      </c>
+      <c r="S19" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="12:19" x14ac:dyDescent="0.2">
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="12:19" x14ac:dyDescent="0.2">
+      <c r="R21">
+        <v>1</v>
+      </c>
+      <c r="S21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="12:19" x14ac:dyDescent="0.2">
+      <c r="R22">
+        <v>2</v>
+      </c>
+      <c r="S22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="12:19" x14ac:dyDescent="0.2">
+      <c r="R23">
+        <v>3</v>
+      </c>
+      <c r="S23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="12:19" x14ac:dyDescent="0.2">
+      <c r="R24">
+        <v>4</v>
+      </c>
+      <c r="S24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="12:19" x14ac:dyDescent="0.2">
+      <c r="R25">
+        <v>5</v>
+      </c>
+      <c r="S25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="12:19" x14ac:dyDescent="0.2">
+      <c r="R26">
+        <v>6</v>
+      </c>
+      <c r="S26">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="12:19" x14ac:dyDescent="0.2">
+      <c r="R27">
+        <v>7</v>
+      </c>
+      <c r="S27">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="12:19" x14ac:dyDescent="0.2">
+      <c r="R28">
+        <v>8</v>
+      </c>
+      <c r="S28">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="12:19" x14ac:dyDescent="0.2">
+      <c r="R29">
+        <v>9</v>
+      </c>
+      <c r="S29">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="12:19" x14ac:dyDescent="0.2">
+      <c r="R30" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="S30" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="12:19" x14ac:dyDescent="0.2">
+      <c r="R31" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="S31" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="12:19" x14ac:dyDescent="0.2">
+      <c r="R32" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="S32" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="18:19" x14ac:dyDescent="0.2">
+      <c r="R33" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="S33" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="18:19" x14ac:dyDescent="0.2">
+      <c r="R34" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="S34" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" spans="18:19" x14ac:dyDescent="0.2">
+      <c r="R35" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="S35" s="4" t="s">
+        <v>33</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="L6:S6"/>
+    <mergeCell ref="T6:AA6"/>
+    <mergeCell ref="AB6:AI6"/>
+    <mergeCell ref="AJ6:AQ6"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
